--- a/research/traditional_assets/database/data/bahrain/bahrain_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0121</v>
+        <v>0.0596</v>
       </c>
       <c r="E2">
-        <v>-0.016185</v>
+        <v>-0.005849999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,103 +600,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0007744212152329888</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.0006688958262047795</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>948.2</v>
+        <v>706.5</v>
       </c>
       <c r="L2">
-        <v>0.2924016282225237</v>
+        <v>0.2254019908116386</v>
       </c>
       <c r="M2">
-        <v>405.402</v>
+        <v>270.934</v>
       </c>
       <c r="N2">
-        <v>0.02363887625511668</v>
+        <v>0.03572536195574778</v>
       </c>
       <c r="O2">
-        <v>0.4275490402868593</v>
+        <v>0.3834876150035386</v>
       </c>
       <c r="P2">
-        <v>351.5</v>
+        <v>263.4</v>
       </c>
       <c r="Q2">
-        <v>0.02049586584100106</v>
+        <v>0.03473192858461457</v>
       </c>
       <c r="R2">
-        <v>0.3707023834634043</v>
+        <v>0.3728237791932059</v>
       </c>
       <c r="S2">
-        <v>53.90199999999999</v>
+        <v>7.533999999999999</v>
       </c>
       <c r="T2">
-        <v>0.1329593835254883</v>
+        <v>0.02780751031616555</v>
       </c>
       <c r="U2">
-        <v>13406.6</v>
+        <v>8703.700000000001</v>
       </c>
       <c r="V2">
-        <v>0.7817350639657605</v>
+        <v>1.147670033492445</v>
       </c>
       <c r="W2">
-        <v>0.06409610819365513</v>
+        <v>0.1101703890677374</v>
       </c>
       <c r="X2">
-        <v>0.1415133108307209</v>
+        <v>0.2748028139217286</v>
       </c>
       <c r="Y2">
-        <v>-0.07741720263706572</v>
+        <v>-0.1646324248539912</v>
       </c>
       <c r="Z2">
-        <v>0.2253375723854554</v>
+        <v>0.4037926414510976</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1016630149767086</v>
+        <v>0.160470276076198</v>
       </c>
       <c r="AC2">
-        <v>-0.1000382924028224</v>
+        <v>-0.160470276076198</v>
       </c>
       <c r="AD2">
-        <v>13922.5</v>
+        <v>9179.9</v>
       </c>
       <c r="AE2">
-        <v>7.35353441621232</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>13929.85353441621</v>
+        <v>9179.9</v>
       </c>
       <c r="AG2">
-        <v>523.2535344162116</v>
+        <v>476.1999999999989</v>
       </c>
       <c r="AH2">
-        <v>0.4481984819744184</v>
+        <v>0.5476058388064687</v>
       </c>
       <c r="AI2">
-        <v>0.4614145638156739</v>
+        <v>0.4685606659963148</v>
       </c>
       <c r="AJ2">
-        <v>0.02960742089063649</v>
+        <v>0.05908188585607928</v>
       </c>
       <c r="AK2">
-        <v>0.03117786455939615</v>
+        <v>0.04373622336517258</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>3496.358613761929</v>
-      </c>
-      <c r="AP2">
-        <v>131.4047047755428</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0814</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.00737</v>
+        <v>-0.00838</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>148.5</v>
+        <v>156.1</v>
       </c>
       <c r="L3">
-        <v>0.4231974921630094</v>
+        <v>0.4134004237288135</v>
       </c>
       <c r="M3">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="N3">
-        <v>0.02952659834065397</v>
+        <v>0.02855977152182783</v>
       </c>
       <c r="O3">
-        <v>0.6518518518518518</v>
+        <v>0.6278026905829597</v>
       </c>
       <c r="P3">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="Q3">
-        <v>0.02952659834065397</v>
+        <v>0.02855977152182783</v>
       </c>
       <c r="R3">
-        <v>0.6518518518518518</v>
+        <v>0.6278026905829597</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1549.9</v>
+        <v>1245.5</v>
       </c>
       <c r="V3">
-        <v>0.472761102977062</v>
+        <v>0.3629713819432301</v>
       </c>
       <c r="W3">
-        <v>0.114477335800185</v>
+        <v>0.1133459192564624</v>
       </c>
       <c r="X3">
-        <v>0.07752148700031043</v>
+        <v>0.1231630888474493</v>
       </c>
       <c r="Y3">
-        <v>0.03695584879987458</v>
+        <v>-0.009817169590986927</v>
       </c>
       <c r="Z3">
-        <v>0.559470663265306</v>
+        <v>1.746530989824238</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07674195366277434</v>
+        <v>0.1237225759435614</v>
       </c>
       <c r="AC3">
-        <v>-0.07674195366277434</v>
+        <v>-0.1237225759435614</v>
       </c>
       <c r="AD3">
-        <v>388.9</v>
+        <v>806.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>388.9</v>
+        <v>806.9</v>
       </c>
       <c r="AG3">
-        <v>-1161</v>
+        <v>-438.6</v>
       </c>
       <c r="AH3">
-        <v>0.1060453194448231</v>
+        <v>0.1903829365547507</v>
       </c>
       <c r="AI3">
-        <v>0.2178833548097932</v>
+        <v>0.357478291688818</v>
       </c>
       <c r="AJ3">
-        <v>-0.5483139699631624</v>
+        <v>-0.146551724137931</v>
       </c>
       <c r="AK3">
-        <v>-4.940425531914894</v>
+        <v>-0.4335277256103588</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ahli United Bank B.S.C. (BAX:AUB)</t>
+          <t>Bank of Bahrain and Kuwait B.S.C. (BAX:BBK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0121</v>
+        <v>0.00563</v>
       </c>
       <c r="E4">
-        <v>-0.025</v>
+        <v>-0.005849999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>493.5</v>
+        <v>151.3</v>
       </c>
       <c r="L4">
-        <v>0.549615770130304</v>
+        <v>0.4843149807938541</v>
       </c>
       <c r="M4">
-        <v>190.2</v>
+        <v>78.7</v>
       </c>
       <c r="N4">
-        <v>0.02018015723971098</v>
+        <v>0.03631078711820614</v>
       </c>
       <c r="O4">
-        <v>0.3854103343465045</v>
+        <v>0.5201586252478519</v>
       </c>
       <c r="P4">
-        <v>151</v>
+        <v>78.7</v>
       </c>
       <c r="Q4">
-        <v>0.01602105017453396</v>
+        <v>0.03631078711820614</v>
       </c>
       <c r="R4">
-        <v>0.3059777102330294</v>
+        <v>0.5201586252478519</v>
       </c>
       <c r="S4">
-        <v>39.19999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.206098843322818</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>3859.1</v>
+        <v>1654.9</v>
       </c>
       <c r="V4">
-        <v>0.4094492366128741</v>
+        <v>0.7635415705453539</v>
       </c>
       <c r="W4">
-        <v>0.1075702421692787</v>
+        <v>0.1074421246981963</v>
       </c>
       <c r="X4">
-        <v>0.1023935014232803</v>
+        <v>0.1617426029957177</v>
       </c>
       <c r="Y4">
-        <v>0.005176740745998401</v>
+        <v>-0.05430047829752147</v>
       </c>
       <c r="Z4">
-        <v>0.2049251415008216</v>
+        <v>0.2114382402707276</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09353394364671277</v>
+        <v>0.1459023631099399</v>
       </c>
       <c r="AC4">
-        <v>-0.09353394364671277</v>
+        <v>-0.1459023631099399</v>
       </c>
       <c r="AD4">
-        <v>5319</v>
+        <v>1733.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5319</v>
+        <v>1733.9</v>
       </c>
       <c r="AG4">
-        <v>1459.9</v>
+        <v>79</v>
       </c>
       <c r="AH4">
-        <v>0.3607544712800374</v>
+        <v>0.4444415963909466</v>
       </c>
       <c r="AI4">
-        <v>0.4717098261794962</v>
+        <v>0.5460758377425045</v>
       </c>
       <c r="AJ4">
-        <v>0.134120349104272</v>
+        <v>0.03516737891737892</v>
       </c>
       <c r="AK4">
-        <v>0.196834256899783</v>
+        <v>0.05196342827073604</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank of Bahrain and Kuwait B.S.C. (BAX:BBK)</t>
+          <t>Al Salam Bank B.S.C. (BAX:SALAM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0149</v>
+        <v>0.104</v>
       </c>
       <c r="E5">
-        <v>-0.007079999999999999</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,85 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>141.9</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L5">
-        <v>0.4587778855480116</v>
+        <v>0.3797183098591549</v>
       </c>
       <c r="M5">
-        <v>69.8</v>
+        <v>31.43</v>
       </c>
       <c r="N5">
-        <v>0.03325709929483514</v>
+        <v>0.04999204708127883</v>
       </c>
       <c r="O5">
-        <v>0.4918957011980267</v>
+        <v>0.466320474777448</v>
       </c>
       <c r="P5">
-        <v>69.8</v>
+        <v>24.2</v>
       </c>
       <c r="Q5">
-        <v>0.03325709929483514</v>
+        <v>0.03849212661046604</v>
       </c>
       <c r="R5">
-        <v>0.4918957011980267</v>
+        <v>0.3590504451038575</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>7.23</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.2300349984091632</v>
       </c>
       <c r="U5">
-        <v>1500.5</v>
+        <v>941.7</v>
       </c>
       <c r="V5">
-        <v>0.7149323422908328</v>
+        <v>1.497852711945284</v>
       </c>
       <c r="W5">
-        <v>0.1175934366453965</v>
+        <v>0.08510101010101011</v>
       </c>
       <c r="X5">
-        <v>0.112639139296946</v>
+        <v>0.2397291747656765</v>
       </c>
       <c r="Y5">
-        <v>0.004954297348450556</v>
+        <v>-0.1546281646646664</v>
       </c>
       <c r="Z5">
-        <v>0.2065304487179487</v>
+        <v>0.3649259868421053</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09446675625359693</v>
+        <v>0.1571363353204546</v>
       </c>
       <c r="AC5">
-        <v>-0.09446675625359693</v>
+        <v>-0.1571363353204546</v>
       </c>
       <c r="AD5">
-        <v>1569.8</v>
+        <v>1220.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1569.8</v>
+        <v>1220.8</v>
       </c>
       <c r="AG5">
-        <v>69.29999999999995</v>
+        <v>279.0999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.4279016518562939</v>
+        <v>0.6600702892673695</v>
       </c>
       <c r="AI5">
-        <v>0.5260547568781208</v>
+        <v>0.586134050316881</v>
       </c>
       <c r="AJ5">
-        <v>0.03196347031963467</v>
+        <v>0.307446574135272</v>
       </c>
       <c r="AK5">
-        <v>0.04671070369371796</v>
+        <v>0.2445885549031636</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Salam Bank B.S.C. (BAX:SALAM)</t>
+          <t>Al Baraka Group B.S.C. (BAX:BARKA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.09089999999999999</v>
+        <v>0.00283</v>
       </c>
       <c r="E6">
-        <v>0.08349999999999999</v>
+        <v>0.0388</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,103 +1088,97 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.0159672302618771</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.0159672302618771</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>45.9</v>
+        <v>159.3</v>
       </c>
       <c r="L6">
-        <v>0.3343044428259286</v>
+        <v>0.1772363150867824</v>
       </c>
       <c r="M6">
-        <v>8.27</v>
+        <v>31.804</v>
       </c>
       <c r="N6">
-        <v>0.01385259631490787</v>
+        <v>0.07874226293637039</v>
       </c>
       <c r="O6">
-        <v>0.1801742919389978</v>
+        <v>0.1996484620213433</v>
       </c>
       <c r="P6">
-        <v>2.4</v>
+        <v>31.5</v>
       </c>
       <c r="Q6">
-        <v>0.004020100502512562</v>
+        <v>0.07798960138648181</v>
       </c>
       <c r="R6">
-        <v>0.05228758169934641</v>
+        <v>0.1977401129943503</v>
       </c>
       <c r="S6">
-        <v>5.869999999999999</v>
+        <v>0.3039999999999985</v>
       </c>
       <c r="T6">
-        <v>0.709794437726723</v>
+        <v>0.009558546094830792</v>
       </c>
       <c r="U6">
-        <v>985.3</v>
+        <v>2507.3</v>
       </c>
       <c r="V6">
-        <v>1.650418760469012</v>
+        <v>6.207724684327805</v>
       </c>
       <c r="W6">
-        <v>0.0593944099378882</v>
+        <v>0.1128986534372785</v>
       </c>
       <c r="X6">
-        <v>0.1415133108307209</v>
+        <v>0.3098764530777807</v>
       </c>
       <c r="Y6">
-        <v>-0.08211890089283266</v>
+        <v>-0.1969777996405022</v>
       </c>
       <c r="Z6">
-        <v>0.1017535632191229</v>
+        <v>2.301075268817205</v>
       </c>
       <c r="AA6">
-        <v>0.001624722573886204</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1016630149767086</v>
+        <v>0.1638042168319413</v>
       </c>
       <c r="AC6">
-        <v>-0.1000382924028224</v>
+        <v>-0.1638042168319413</v>
       </c>
       <c r="AD6">
-        <v>748.6</v>
+        <v>1199.1</v>
       </c>
       <c r="AE6">
-        <v>6.838496425221376</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>755.4384964252214</v>
+        <v>1199.1</v>
       </c>
       <c r="AG6">
-        <v>-229.8615035747786</v>
+        <v>-1308.2</v>
       </c>
       <c r="AH6">
-        <v>0.558575120733404</v>
+        <v>0.7480349344978166</v>
       </c>
       <c r="AI6">
-        <v>0.4876821965164696</v>
+        <v>0.3725185622417596</v>
       </c>
       <c r="AJ6">
-        <v>-0.6260893526909037</v>
+        <v>1.446643812893951</v>
       </c>
       <c r="AK6">
-        <v>-0.4077449119270306</v>
+        <v>-1.838392355255763</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>210.2808988764045</v>
-      </c>
-      <c r="AP6">
-        <v>-64.56783808280296</v>
       </c>
     </row>
     <row r="7">
@@ -1201,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arab Banking Corporation (B.S.C.) (BAX:ABC)</t>
+          <t>Ithmaar Holding B.S.C. (BAX:ITHMR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,10 +1198,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0304</v>
-      </c>
-      <c r="E7">
-        <v>-0.241</v>
+        <v>0.216</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>47</v>
+        <v>38.4</v>
       </c>
       <c r="L7">
-        <v>0.07004470938897168</v>
+        <v>0.08437705998681608</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1255,55 +1240,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2249</v>
+        <v>332.3</v>
       </c>
       <c r="V7">
-        <v>1.943484272381611</v>
+        <v>2.854810996563574</v>
       </c>
       <c r="W7">
-        <v>0.0127891156462585</v>
+        <v>3.2</v>
       </c>
       <c r="X7">
-        <v>0.2138306618714733</v>
+        <v>0.8559570572670649</v>
       </c>
       <c r="Y7">
-        <v>-0.2010415462252148</v>
+        <v>2.344042942732935</v>
       </c>
       <c r="Z7">
-        <v>0.1326611308817714</v>
+        <v>0.73796011026431</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1171646242907858</v>
+        <v>0.1765677603886705</v>
       </c>
       <c r="AC7">
-        <v>-0.1171646242907858</v>
+        <v>-0.1765677603886705</v>
       </c>
       <c r="AD7">
-        <v>2964</v>
+        <v>1276.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2964</v>
+        <v>1276.2</v>
       </c>
       <c r="AG7">
-        <v>715</v>
+        <v>943.9000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.7192079976705814</v>
+        <v>0.9164153382162861</v>
       </c>
       <c r="AI7">
-        <v>0.4120672876407618</v>
+        <v>0.8996193430142393</v>
       </c>
       <c r="AJ7">
-        <v>0.381903642773208</v>
+        <v>0.8902197491276054</v>
       </c>
       <c r="AK7">
-        <v>0.1446197411003236</v>
+        <v>0.8689128233453005</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1320,7 +1305,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bahrain Islamic Bank B.S.C. (BAX:BISB)</t>
+          <t>Arab Banking Corporation (B.S.C.) (BAX:ABC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1329,7 +1314,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.126</v>
+        <v>0.0371</v>
+      </c>
+      <c r="E8">
+        <v>-0.06150000000000001</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,224 +1326,96 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.007523405702872903</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.007523405702872903</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>-17.7</v>
+        <v>134</v>
       </c>
       <c r="L8">
-        <v>-0.4174528301886792</v>
+        <v>0.1467688937568456</v>
       </c>
       <c r="M8">
-        <v>0.302</v>
+        <v>31</v>
       </c>
       <c r="N8">
-        <v>0.001311902693310165</v>
+        <v>0.03708133971291866</v>
       </c>
       <c r="O8">
-        <v>-0.01706214689265537</v>
+        <v>0.2313432835820896</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>31</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.03708133971291866</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.2313432835820896</v>
       </c>
       <c r="S8">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>337.3</v>
+        <v>2022</v>
       </c>
       <c r="V8">
-        <v>1.465247610773241</v>
+        <v>2.41866028708134</v>
       </c>
       <c r="W8">
-        <v>-0.06382978723404255</v>
+        <v>0.03471502590673575</v>
       </c>
       <c r="X8">
-        <v>0.3200025637979216</v>
+        <v>0.3475469952761114</v>
       </c>
       <c r="Y8">
-        <v>-0.3838323510319642</v>
+        <v>-0.3128319693693756</v>
       </c>
       <c r="Z8">
-        <v>0.03800594161616384</v>
+        <v>0.1995628415300547</v>
       </c>
       <c r="AA8">
-        <v>0.0002859341178981016</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1221555566815211</v>
+        <v>0.1767259296244586</v>
       </c>
       <c r="AC8">
-        <v>-0.121869622563623</v>
+        <v>-0.1767259296244586</v>
       </c>
       <c r="AD8">
-        <v>1027.1</v>
+        <v>2943</v>
       </c>
       <c r="AE8">
-        <v>0.5150379909909446</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1027.615037990991</v>
+        <v>2943</v>
       </c>
       <c r="AG8">
-        <v>690.315037990991</v>
+        <v>921</v>
       </c>
       <c r="AH8">
-        <v>0.8169842202175605</v>
+        <v>0.7787774543530035</v>
       </c>
       <c r="AI8">
-        <v>0.7580993269643244</v>
+        <v>0.3956176905498051</v>
       </c>
       <c r="AJ8">
-        <v>0.7499226079973579</v>
+        <v>0.5241889584519066</v>
       </c>
       <c r="AK8">
-        <v>0.6779658640212489</v>
+        <v>0.1700203064426805</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>2433.886255924171</v>
-      </c>
-      <c r="AP8">
-        <v>1635.817625571069</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Al Baraka Banking Group B.S.C. (BAX:BARKA)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>-0.0265</v>
-      </c>
-      <c r="E9">
-        <v>-0.108</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="L9">
-        <v>0.1068345323741007</v>
-      </c>
-      <c r="M9">
-        <v>40.03</v>
-      </c>
-      <c r="N9">
-        <v>0.1102451115395208</v>
-      </c>
-      <c r="O9">
-        <v>0.449270482603816</v>
-      </c>
-      <c r="P9">
-        <v>31.5</v>
-      </c>
-      <c r="Q9">
-        <v>0.08675296061690993</v>
-      </c>
-      <c r="R9">
-        <v>0.3535353535353535</v>
-      </c>
-      <c r="S9">
-        <v>8.530000000000001</v>
-      </c>
-      <c r="T9">
-        <v>0.2130901823632276</v>
-      </c>
-      <c r="U9">
-        <v>2925.5</v>
-      </c>
-      <c r="V9">
-        <v>8.057009088405398</v>
-      </c>
-      <c r="W9">
-        <v>0.06409610819365513</v>
-      </c>
-      <c r="X9">
-        <v>0.3636818014449007</v>
-      </c>
-      <c r="Y9">
-        <v>-0.2995856932512456</v>
-      </c>
-      <c r="Z9">
-        <v>2.307053941908713</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.1337482990438305</v>
-      </c>
-      <c r="AC9">
-        <v>-0.1337482990438305</v>
-      </c>
-      <c r="AD9">
-        <v>1905.1</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>1905.1</v>
-      </c>
-      <c r="AG9">
-        <v>-1020.4</v>
-      </c>
-      <c r="AH9">
-        <v>0.8399171148928666</v>
-      </c>
-      <c r="AI9">
-        <v>0.4707553930168771</v>
-      </c>
-      <c r="AJ9">
-        <v>1.552411379887418</v>
-      </c>
-      <c r="AK9">
-        <v>-0.9099340110576065</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/bahrain/bahrain_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0596</v>
+        <v>0.101</v>
       </c>
       <c r="E2">
-        <v>-0.005849999999999999</v>
+        <v>0.03475</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>706.5</v>
+        <v>506.8</v>
       </c>
       <c r="L2">
-        <v>0.2254019908116386</v>
+        <v>0.3314367928847035</v>
       </c>
       <c r="M2">
-        <v>270.934</v>
+        <v>418.309</v>
       </c>
       <c r="N2">
-        <v>0.03572536195574778</v>
+        <v>0.05566468834832596</v>
       </c>
       <c r="O2">
-        <v>0.3834876150035386</v>
+        <v>0.8253926598263615</v>
       </c>
       <c r="P2">
-        <v>263.4</v>
+        <v>410.55</v>
       </c>
       <c r="Q2">
-        <v>0.03473192858461457</v>
+        <v>0.05463219247351892</v>
       </c>
       <c r="R2">
-        <v>0.3728237791932059</v>
+        <v>0.8100828729281768</v>
       </c>
       <c r="S2">
-        <v>7.533999999999999</v>
+        <v>7.758999999999998</v>
       </c>
       <c r="T2">
-        <v>0.02780751031616555</v>
+        <v>0.01854848927467494</v>
       </c>
       <c r="U2">
-        <v>8703.700000000001</v>
+        <v>5754.900000000001</v>
       </c>
       <c r="V2">
-        <v>1.147670033492445</v>
+        <v>0.7658088039601852</v>
       </c>
       <c r="W2">
-        <v>0.1101703890677374</v>
+        <v>0.1413240418118467</v>
       </c>
       <c r="X2">
-        <v>0.2748028139217286</v>
+        <v>0.1475917833975463</v>
       </c>
       <c r="Y2">
-        <v>-0.1646324248539912</v>
+        <v>-0.006267741585699649</v>
       </c>
       <c r="Z2">
-        <v>0.4037926414510976</v>
+        <v>0.2575768805756947</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.160470276076198</v>
+        <v>0.1244689619995818</v>
       </c>
       <c r="AC2">
-        <v>-0.160470276076198</v>
+        <v>-0.1244689619995818</v>
       </c>
       <c r="AD2">
-        <v>9179.9</v>
+        <v>7138</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9179.9</v>
+        <v>7138</v>
       </c>
       <c r="AG2">
-        <v>476.1999999999989</v>
+        <v>1383.099999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5476058388064687</v>
+        <v>0.4871423891679406</v>
       </c>
       <c r="AI2">
-        <v>0.4685606659963148</v>
+        <v>0.6064210284859863</v>
       </c>
       <c r="AJ2">
-        <v>0.05908188585607928</v>
+        <v>0.1554411715123793</v>
       </c>
       <c r="AK2">
-        <v>0.04373622336517258</v>
+        <v>0.229911233751122</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Bank of Bahrain BSC (BAX:NBB)</t>
+          <t>The National Bank of Bahrain B.S.C. (BAX:NBB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08210000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="E3">
-        <v>-0.00838</v>
+        <v>0.0276</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>156.1</v>
+        <v>202.6</v>
       </c>
       <c r="L3">
-        <v>0.4134004237288135</v>
+        <v>0.4411060309166122</v>
       </c>
       <c r="M3">
-        <v>98</v>
+        <v>196.7</v>
       </c>
       <c r="N3">
-        <v>0.02855977152182783</v>
+        <v>0.05498560366757051</v>
       </c>
       <c r="O3">
-        <v>0.6278026905829597</v>
+        <v>0.970878578479763</v>
       </c>
       <c r="P3">
-        <v>98</v>
+        <v>196.7</v>
       </c>
       <c r="Q3">
-        <v>0.02855977152182783</v>
+        <v>0.05498560366757051</v>
       </c>
       <c r="R3">
-        <v>0.6278026905829597</v>
+        <v>0.970878578479763</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1245.5</v>
+        <v>1968.9</v>
       </c>
       <c r="V3">
-        <v>0.3629713819432301</v>
+        <v>0.5503871635032007</v>
       </c>
       <c r="W3">
-        <v>0.1133459192564624</v>
+        <v>0.1421355409007998</v>
       </c>
       <c r="X3">
-        <v>0.1231630888474493</v>
+        <v>0.1017210066902732</v>
       </c>
       <c r="Y3">
-        <v>-0.009817169590986927</v>
+        <v>0.04041453421052657</v>
       </c>
       <c r="Z3">
-        <v>1.746530989824238</v>
+        <v>0.4654438589379813</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1237225759435614</v>
+        <v>0.1041715159598382</v>
       </c>
       <c r="AC3">
-        <v>-0.1237225759435614</v>
+        <v>-0.1041715159598382</v>
       </c>
       <c r="AD3">
-        <v>806.9</v>
+        <v>944.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>806.9</v>
+        <v>944.9</v>
       </c>
       <c r="AG3">
-        <v>-438.6</v>
+        <v>-1024</v>
       </c>
       <c r="AH3">
-        <v>0.1903829365547507</v>
+        <v>0.2089469727123966</v>
       </c>
       <c r="AI3">
-        <v>0.357478291688818</v>
+        <v>0.38595702965444</v>
       </c>
       <c r="AJ3">
-        <v>-0.146551724137931</v>
+        <v>-0.4010496220577292</v>
       </c>
       <c r="AK3">
-        <v>-0.4335277256103588</v>
+        <v>-2.136448988107657</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00563</v>
+        <v>0.062</v>
       </c>
       <c r="E4">
-        <v>-0.005849999999999999</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>151.3</v>
+        <v>202.8</v>
       </c>
       <c r="L4">
-        <v>0.4843149807938541</v>
+        <v>0.499261447562777</v>
       </c>
       <c r="M4">
-        <v>78.7</v>
+        <v>176</v>
       </c>
       <c r="N4">
-        <v>0.03631078711820614</v>
+        <v>0.07663836272588721</v>
       </c>
       <c r="O4">
-        <v>0.5201586252478519</v>
+        <v>0.8678500986193294</v>
       </c>
       <c r="P4">
-        <v>78.7</v>
+        <v>176</v>
       </c>
       <c r="Q4">
-        <v>0.03631078711820614</v>
+        <v>0.07663836272588721</v>
       </c>
       <c r="R4">
-        <v>0.5201586252478519</v>
+        <v>0.8678500986193294</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1654.9</v>
+        <v>2062.9</v>
       </c>
       <c r="V4">
-        <v>0.7635415705453539</v>
+        <v>0.8982799912910951</v>
       </c>
       <c r="W4">
-        <v>0.1074421246981963</v>
+        <v>0.1413240418118467</v>
       </c>
       <c r="X4">
-        <v>0.1617426029957177</v>
+        <v>0.1260868440981259</v>
       </c>
       <c r="Y4">
-        <v>-0.05430047829752147</v>
+        <v>0.01523719771372081</v>
       </c>
       <c r="Z4">
-        <v>0.2114382402707276</v>
+        <v>0.2682959048877147</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1459023631099399</v>
+        <v>0.120655477798167</v>
       </c>
       <c r="AC4">
-        <v>-0.1459023631099399</v>
+        <v>-0.120655477798167</v>
       </c>
       <c r="AD4">
-        <v>1733.9</v>
+        <v>1730.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1733.9</v>
+        <v>1730.8</v>
       </c>
       <c r="AG4">
-        <v>79</v>
+        <v>-332.1000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.4444415963909466</v>
+        <v>0.4297668413080724</v>
       </c>
       <c r="AI4">
-        <v>0.5460758377425045</v>
+        <v>0.5249620867455262</v>
       </c>
       <c r="AJ4">
-        <v>0.03516737891737892</v>
+        <v>-0.1690592547342701</v>
       </c>
       <c r="AK4">
-        <v>0.05196342827073604</v>
+        <v>-0.2691029900332227</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.104</v>
+        <v>0.193</v>
       </c>
       <c r="E5">
-        <v>0.08349999999999999</v>
+        <v>0.187</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,85 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>67.40000000000001</v>
+        <v>112.3</v>
       </c>
       <c r="L5">
-        <v>0.3797183098591549</v>
+        <v>0.4171619613670134</v>
       </c>
       <c r="M5">
-        <v>31.43</v>
+        <v>40.48999999999999</v>
       </c>
       <c r="N5">
-        <v>0.04999204708127883</v>
+        <v>0.02946655993013609</v>
       </c>
       <c r="O5">
-        <v>0.466320474777448</v>
+        <v>0.3605520926090828</v>
       </c>
       <c r="P5">
-        <v>24.2</v>
+        <v>32.8</v>
       </c>
       <c r="Q5">
-        <v>0.03849212661046604</v>
+        <v>0.0238701695655338</v>
       </c>
       <c r="R5">
-        <v>0.3590504451038575</v>
+        <v>0.2920747996438112</v>
       </c>
       <c r="S5">
-        <v>7.23</v>
+        <v>7.689999999999998</v>
       </c>
       <c r="T5">
-        <v>0.2300349984091632</v>
+        <v>0.1899234378858977</v>
       </c>
       <c r="U5">
-        <v>941.7</v>
+        <v>1057.8</v>
       </c>
       <c r="V5">
-        <v>1.497852711945284</v>
+        <v>0.7698129684884651</v>
       </c>
       <c r="W5">
-        <v>0.08510101010101011</v>
+        <v>0.1452969336266011</v>
       </c>
       <c r="X5">
-        <v>0.2397291747656765</v>
+        <v>0.1475917833975463</v>
       </c>
       <c r="Y5">
-        <v>-0.1546281646646664</v>
+        <v>-0.002294849770945212</v>
       </c>
       <c r="Z5">
-        <v>0.3649259868421053</v>
+        <v>0.255893536121673</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1571363353204546</v>
+        <v>0.1244689619995818</v>
       </c>
       <c r="AC5">
-        <v>-0.1571363353204546</v>
+        <v>-0.1244689619995818</v>
       </c>
       <c r="AD5">
-        <v>1220.8</v>
+        <v>1629.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1220.8</v>
+        <v>1629.3</v>
       </c>
       <c r="AG5">
-        <v>279.0999999999999</v>
+        <v>571.5</v>
       </c>
       <c r="AH5">
-        <v>0.6600702892673695</v>
+        <v>0.5424851834587469</v>
       </c>
       <c r="AI5">
-        <v>0.586134050316881</v>
+        <v>0.607381174277726</v>
       </c>
       <c r="AJ5">
-        <v>0.307446574135272</v>
+        <v>0.2937397203947368</v>
       </c>
       <c r="AK5">
-        <v>0.2445885549031636</v>
+        <v>0.3517572474918446</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Baraka Group B.S.C. (BAX:BARKA)</t>
+          <t>Bahrain Islamic Bank B.S.C. (BAX:BISB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00283</v>
+        <v>0.0209</v>
       </c>
       <c r="E6">
-        <v>0.0388</v>
+        <v>0.0161</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,85 +1094,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>159.3</v>
+        <v>33.3</v>
       </c>
       <c r="L6">
-        <v>0.1772363150867824</v>
+        <v>0.3038321167883212</v>
       </c>
       <c r="M6">
-        <v>31.804</v>
+        <v>5.119</v>
       </c>
       <c r="N6">
-        <v>0.07874226293637039</v>
+        <v>0.0285022271714922</v>
       </c>
       <c r="O6">
-        <v>0.1996484620213433</v>
+        <v>0.1537237237237237</v>
       </c>
       <c r="P6">
-        <v>31.5</v>
+        <v>5.05</v>
       </c>
       <c r="Q6">
-        <v>0.07798960138648181</v>
+        <v>0.02811804008908686</v>
       </c>
       <c r="R6">
-        <v>0.1977401129943503</v>
+        <v>0.1516516516516516</v>
       </c>
       <c r="S6">
-        <v>0.3039999999999985</v>
+        <v>0.06899999999999995</v>
       </c>
       <c r="T6">
-        <v>0.009558546094830792</v>
+        <v>0.01347919515530376</v>
       </c>
       <c r="U6">
-        <v>2507.3</v>
+        <v>325</v>
       </c>
       <c r="V6">
-        <v>6.207724684327805</v>
+        <v>1.809576837416481</v>
       </c>
       <c r="W6">
-        <v>0.1128986534372785</v>
+        <v>0.09473684210526315</v>
       </c>
       <c r="X6">
-        <v>0.3098764530777807</v>
+        <v>0.5845109888220408</v>
       </c>
       <c r="Y6">
-        <v>-0.1969777996405022</v>
+        <v>-0.4897741467167777</v>
       </c>
       <c r="Z6">
-        <v>2.301075268817205</v>
+        <v>0.07645622602023021</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1638042168319413</v>
+        <v>0.1487066391750316</v>
       </c>
       <c r="AC6">
-        <v>-0.1638042168319413</v>
+        <v>-0.1487066391750316</v>
       </c>
       <c r="AD6">
-        <v>1199.1</v>
+        <v>1789.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1199.1</v>
+        <v>1789.5</v>
       </c>
       <c r="AG6">
-        <v>-1308.2</v>
+        <v>1464.5</v>
       </c>
       <c r="AH6">
-        <v>0.7480349344978166</v>
+        <v>0.9087908181402672</v>
       </c>
       <c r="AI6">
-        <v>0.3725185622417596</v>
+        <v>0.825110660272962</v>
       </c>
       <c r="AJ6">
-        <v>1.446643812893951</v>
+        <v>0.8907609026214951</v>
       </c>
       <c r="AK6">
-        <v>-1.838392355255763</v>
+        <v>0.794283544853021</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.216</v>
+        <v>0.101</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1213,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>38.4</v>
+        <v>-44.2</v>
       </c>
       <c r="L7">
-        <v>0.08437705998681608</v>
+        <v>-0.1551966292134832</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1225,7 +1225,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1234,188 +1234,66 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>332.3</v>
+        <v>340.3</v>
       </c>
       <c r="V7">
-        <v>2.854810996563574</v>
+        <v>3.898052691867125</v>
       </c>
       <c r="W7">
-        <v>3.2</v>
+        <v>-7.038216560509555</v>
       </c>
       <c r="X7">
-        <v>0.8559570572670649</v>
+        <v>0.6835224830639652</v>
       </c>
       <c r="Y7">
-        <v>2.344042942732935</v>
+        <v>-7.721739043573519</v>
       </c>
       <c r="Z7">
-        <v>0.73796011026431</v>
+        <v>0.2997326822286304</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1765677603886705</v>
+        <v>0.1574597163458059</v>
       </c>
       <c r="AC7">
-        <v>-0.1765677603886705</v>
+        <v>-0.1574597163458059</v>
       </c>
       <c r="AD7">
-        <v>1276.2</v>
+        <v>1043.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1276.2</v>
+        <v>1043.5</v>
       </c>
       <c r="AG7">
-        <v>943.9000000000001</v>
+        <v>703.2</v>
       </c>
       <c r="AH7">
-        <v>0.9164153382162861</v>
+        <v>0.922798019101521</v>
       </c>
       <c r="AI7">
-        <v>0.8996193430142393</v>
+        <v>0.8886901720320217</v>
       </c>
       <c r="AJ7">
-        <v>0.8902197491276054</v>
+        <v>0.8895635673624289</v>
       </c>
       <c r="AK7">
-        <v>0.8689128233453005</v>
+        <v>0.8432665787264659</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Arab Banking Corporation (B.S.C.) (BAX:ABC)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0371</v>
-      </c>
-      <c r="E8">
-        <v>-0.06150000000000001</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>134</v>
-      </c>
-      <c r="L8">
-        <v>0.1467688937568456</v>
-      </c>
-      <c r="M8">
-        <v>31</v>
-      </c>
-      <c r="N8">
-        <v>0.03708133971291866</v>
-      </c>
-      <c r="O8">
-        <v>0.2313432835820896</v>
-      </c>
-      <c r="P8">
-        <v>31</v>
-      </c>
-      <c r="Q8">
-        <v>0.03708133971291866</v>
-      </c>
-      <c r="R8">
-        <v>0.2313432835820896</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>2022</v>
-      </c>
-      <c r="V8">
-        <v>2.41866028708134</v>
-      </c>
-      <c r="W8">
-        <v>0.03471502590673575</v>
-      </c>
-      <c r="X8">
-        <v>0.3475469952761114</v>
-      </c>
-      <c r="Y8">
-        <v>-0.3128319693693756</v>
-      </c>
-      <c r="Z8">
-        <v>0.1995628415300547</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.1767259296244586</v>
-      </c>
-      <c r="AC8">
-        <v>-0.1767259296244586</v>
-      </c>
-      <c r="AD8">
-        <v>2943</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>2943</v>
-      </c>
-      <c r="AG8">
-        <v>921</v>
-      </c>
-      <c r="AH8">
-        <v>0.7787774543530035</v>
-      </c>
-      <c r="AI8">
-        <v>0.3956176905498051</v>
-      </c>
-      <c r="AJ8">
-        <v>0.5241889584519066</v>
-      </c>
-      <c r="AK8">
-        <v>0.1700203064426805</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/bahrain/bahrain_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.101</v>
+        <v>0.0851</v>
       </c>
       <c r="E2">
-        <v>0.03475</v>
+        <v>0.0553</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>506.8</v>
+        <v>267</v>
       </c>
       <c r="L2">
-        <v>0.3314367928847035</v>
+        <v>0.2232441471571906</v>
       </c>
       <c r="M2">
-        <v>418.309</v>
+        <v>88</v>
       </c>
       <c r="N2">
-        <v>0.05566468834832596</v>
+        <v>0.08488473039452107</v>
       </c>
       <c r="O2">
-        <v>0.8253926598263615</v>
+        <v>0.3295880149812734</v>
       </c>
       <c r="P2">
-        <v>410.55</v>
+        <v>88</v>
       </c>
       <c r="Q2">
-        <v>0.05463219247351892</v>
+        <v>0.08488473039452107</v>
       </c>
       <c r="R2">
-        <v>0.8100828729281768</v>
+        <v>0.3295880149812734</v>
       </c>
       <c r="S2">
-        <v>7.758999999999998</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.01854848927467494</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>5754.900000000001</v>
+        <v>1992</v>
       </c>
       <c r="V2">
-        <v>0.7658088039601852</v>
+        <v>1.921481624385068</v>
       </c>
       <c r="W2">
-        <v>0.1413240418118467</v>
+        <v>0.06340536689622417</v>
       </c>
       <c r="X2">
-        <v>0.1475917833975463</v>
+        <v>0.5394781954200573</v>
       </c>
       <c r="Y2">
-        <v>-0.006267741585699649</v>
+        <v>-0.4760728285238331</v>
       </c>
       <c r="Z2">
-        <v>0.2575768805756947</v>
+        <v>0.1238351625595361</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1244689619995818</v>
+        <v>0.1538550080513593</v>
       </c>
       <c r="AC2">
-        <v>-0.1244689619995818</v>
+        <v>-0.1538550080513593</v>
       </c>
       <c r="AD2">
-        <v>7138</v>
+        <v>10101</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7138</v>
+        <v>10101</v>
       </c>
       <c r="AG2">
-        <v>1383.099999999999</v>
+        <v>8109</v>
       </c>
       <c r="AH2">
-        <v>0.4871423891679406</v>
+        <v>0.9069197410596442</v>
       </c>
       <c r="AI2">
-        <v>0.6064210284859863</v>
+        <v>0.6806603773584906</v>
       </c>
       <c r="AJ2">
-        <v>0.1554411715123793</v>
+        <v>0.8866461834523327</v>
       </c>
       <c r="AK2">
-        <v>0.229911233751122</v>
+        <v>0.6311488169364882</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The National Bank of Bahrain B.S.C. (BAX:NBB)</t>
+          <t>Arab Banking Corporation (B.S.C.) (BAX:ABC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.102</v>
+        <v>0.0851</v>
       </c>
       <c r="E3">
-        <v>0.0276</v>
+        <v>0.0553</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>202.6</v>
+        <v>267</v>
       </c>
       <c r="L3">
-        <v>0.4411060309166122</v>
+        <v>0.2232441471571906</v>
       </c>
       <c r="M3">
-        <v>196.7</v>
+        <v>88</v>
       </c>
       <c r="N3">
-        <v>0.05498560366757051</v>
+        <v>0.08488473039452107</v>
       </c>
       <c r="O3">
-        <v>0.970878578479763</v>
+        <v>0.3295880149812734</v>
       </c>
       <c r="P3">
-        <v>196.7</v>
+        <v>88</v>
       </c>
       <c r="Q3">
-        <v>0.05498560366757051</v>
+        <v>0.08488473039452107</v>
       </c>
       <c r="R3">
-        <v>0.970878578479763</v>
+        <v>0.3295880149812734</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,542 +758,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1968.9</v>
+        <v>1992</v>
       </c>
       <c r="V3">
-        <v>0.5503871635032007</v>
+        <v>1.921481624385068</v>
       </c>
       <c r="W3">
-        <v>0.1421355409007998</v>
+        <v>0.06340536689622417</v>
       </c>
       <c r="X3">
-        <v>0.1017210066902732</v>
+        <v>0.5394781954200573</v>
       </c>
       <c r="Y3">
-        <v>0.04041453421052657</v>
+        <v>-0.4760728285238331</v>
       </c>
       <c r="Z3">
-        <v>0.4654438589379813</v>
+        <v>0.1238351625595361</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1041715159598382</v>
+        <v>0.1538550080513593</v>
       </c>
       <c r="AC3">
-        <v>-0.1041715159598382</v>
+        <v>-0.1538550080513593</v>
       </c>
       <c r="AD3">
-        <v>944.9</v>
+        <v>10101</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>944.9</v>
+        <v>10101</v>
       </c>
       <c r="AG3">
-        <v>-1024</v>
+        <v>8109</v>
       </c>
       <c r="AH3">
-        <v>0.2089469727123966</v>
+        <v>0.9069197410596442</v>
       </c>
       <c r="AI3">
-        <v>0.38595702965444</v>
+        <v>0.6806603773584906</v>
       </c>
       <c r="AJ3">
-        <v>-0.4010496220577292</v>
+        <v>0.8866461834523327</v>
       </c>
       <c r="AK3">
-        <v>-2.136448988107657</v>
+        <v>0.6311488169364882</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bank of Bahrain and Kuwait B.S.C. (BAX:BBK)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.062</v>
-      </c>
-      <c r="E4">
-        <v>0.04190000000000001</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>202.8</v>
-      </c>
-      <c r="L4">
-        <v>0.499261447562777</v>
-      </c>
-      <c r="M4">
-        <v>176</v>
-      </c>
-      <c r="N4">
-        <v>0.07663836272588721</v>
-      </c>
-      <c r="O4">
-        <v>0.8678500986193294</v>
-      </c>
-      <c r="P4">
-        <v>176</v>
-      </c>
-      <c r="Q4">
-        <v>0.07663836272588721</v>
-      </c>
-      <c r="R4">
-        <v>0.8678500986193294</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>2062.9</v>
-      </c>
-      <c r="V4">
-        <v>0.8982799912910951</v>
-      </c>
-      <c r="W4">
-        <v>0.1413240418118467</v>
-      </c>
-      <c r="X4">
-        <v>0.1260868440981259</v>
-      </c>
-      <c r="Y4">
-        <v>0.01523719771372081</v>
-      </c>
-      <c r="Z4">
-        <v>0.2682959048877147</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.120655477798167</v>
-      </c>
-      <c r="AC4">
-        <v>-0.120655477798167</v>
-      </c>
-      <c r="AD4">
-        <v>1730.8</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>1730.8</v>
-      </c>
-      <c r="AG4">
-        <v>-332.1000000000001</v>
-      </c>
-      <c r="AH4">
-        <v>0.4297668413080724</v>
-      </c>
-      <c r="AI4">
-        <v>0.5249620867455262</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.1690592547342701</v>
-      </c>
-      <c r="AK4">
-        <v>-0.2691029900332227</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Al Salam Bank B.S.C. (BAX:SALAM)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.193</v>
-      </c>
-      <c r="E5">
-        <v>0.187</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>112.3</v>
-      </c>
-      <c r="L5">
-        <v>0.4171619613670134</v>
-      </c>
-      <c r="M5">
-        <v>40.48999999999999</v>
-      </c>
-      <c r="N5">
-        <v>0.02946655993013609</v>
-      </c>
-      <c r="O5">
-        <v>0.3605520926090828</v>
-      </c>
-      <c r="P5">
-        <v>32.8</v>
-      </c>
-      <c r="Q5">
-        <v>0.0238701695655338</v>
-      </c>
-      <c r="R5">
-        <v>0.2920747996438112</v>
-      </c>
-      <c r="S5">
-        <v>7.689999999999998</v>
-      </c>
-      <c r="T5">
-        <v>0.1899234378858977</v>
-      </c>
-      <c r="U5">
-        <v>1057.8</v>
-      </c>
-      <c r="V5">
-        <v>0.7698129684884651</v>
-      </c>
-      <c r="W5">
-        <v>0.1452969336266011</v>
-      </c>
-      <c r="X5">
-        <v>0.1475917833975463</v>
-      </c>
-      <c r="Y5">
-        <v>-0.002294849770945212</v>
-      </c>
-      <c r="Z5">
-        <v>0.255893536121673</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.1244689619995818</v>
-      </c>
-      <c r="AC5">
-        <v>-0.1244689619995818</v>
-      </c>
-      <c r="AD5">
-        <v>1629.3</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>1629.3</v>
-      </c>
-      <c r="AG5">
-        <v>571.5</v>
-      </c>
-      <c r="AH5">
-        <v>0.5424851834587469</v>
-      </c>
-      <c r="AI5">
-        <v>0.607381174277726</v>
-      </c>
-      <c r="AJ5">
-        <v>0.2937397203947368</v>
-      </c>
-      <c r="AK5">
-        <v>0.3517572474918446</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bahrain Islamic Bank B.S.C. (BAX:BISB)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0209</v>
-      </c>
-      <c r="E6">
-        <v>0.0161</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>33.3</v>
-      </c>
-      <c r="L6">
-        <v>0.3038321167883212</v>
-      </c>
-      <c r="M6">
-        <v>5.119</v>
-      </c>
-      <c r="N6">
-        <v>0.0285022271714922</v>
-      </c>
-      <c r="O6">
-        <v>0.1537237237237237</v>
-      </c>
-      <c r="P6">
-        <v>5.05</v>
-      </c>
-      <c r="Q6">
-        <v>0.02811804008908686</v>
-      </c>
-      <c r="R6">
-        <v>0.1516516516516516</v>
-      </c>
-      <c r="S6">
-        <v>0.06899999999999995</v>
-      </c>
-      <c r="T6">
-        <v>0.01347919515530376</v>
-      </c>
-      <c r="U6">
-        <v>325</v>
-      </c>
-      <c r="V6">
-        <v>1.809576837416481</v>
-      </c>
-      <c r="W6">
-        <v>0.09473684210526315</v>
-      </c>
-      <c r="X6">
-        <v>0.5845109888220408</v>
-      </c>
-      <c r="Y6">
-        <v>-0.4897741467167777</v>
-      </c>
-      <c r="Z6">
-        <v>0.07645622602023021</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.1487066391750316</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1487066391750316</v>
-      </c>
-      <c r="AD6">
-        <v>1789.5</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>1789.5</v>
-      </c>
-      <c r="AG6">
-        <v>1464.5</v>
-      </c>
-      <c r="AH6">
-        <v>0.9087908181402672</v>
-      </c>
-      <c r="AI6">
-        <v>0.825110660272962</v>
-      </c>
-      <c r="AJ6">
-        <v>0.8907609026214951</v>
-      </c>
-      <c r="AK6">
-        <v>0.794283544853021</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ithmaar Holding B.S.C. (BAX:ITHMR)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.101</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>-44.2</v>
-      </c>
-      <c r="L7">
-        <v>-0.1551966292134832</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>340.3</v>
-      </c>
-      <c r="V7">
-        <v>3.898052691867125</v>
-      </c>
-      <c r="W7">
-        <v>-7.038216560509555</v>
-      </c>
-      <c r="X7">
-        <v>0.6835224830639652</v>
-      </c>
-      <c r="Y7">
-        <v>-7.721739043573519</v>
-      </c>
-      <c r="Z7">
-        <v>0.2997326822286304</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.1574597163458059</v>
-      </c>
-      <c r="AC7">
-        <v>-0.1574597163458059</v>
-      </c>
-      <c r="AD7">
-        <v>1043.5</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>1043.5</v>
-      </c>
-      <c r="AG7">
-        <v>703.2</v>
-      </c>
-      <c r="AH7">
-        <v>0.922798019101521</v>
-      </c>
-      <c r="AI7">
-        <v>0.8886901720320217</v>
-      </c>
-      <c r="AJ7">
-        <v>0.8895635673624289</v>
-      </c>
-      <c r="AK7">
-        <v>0.8432665787264659</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/bahrain/bahrain_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0851</v>
+        <v>0.09755</v>
       </c>
       <c r="E2">
-        <v>0.0553</v>
+        <v>0.0386</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>267</v>
+        <v>857.5</v>
       </c>
       <c r="L2">
-        <v>0.2232441471571906</v>
+        <v>0.3130590339892665</v>
       </c>
       <c r="M2">
-        <v>88</v>
+        <v>577.403</v>
       </c>
       <c r="N2">
-        <v>0.08488473039452107</v>
+        <v>0.07135744034010159</v>
       </c>
       <c r="O2">
-        <v>0.3295880149812734</v>
+        <v>0.6733562682215744</v>
       </c>
       <c r="P2">
-        <v>88</v>
+        <v>486.22</v>
       </c>
       <c r="Q2">
-        <v>0.08488473039452107</v>
+        <v>0.06008873289914356</v>
       </c>
       <c r="R2">
-        <v>0.3295880149812734</v>
+        <v>0.5670204081632653</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>91.18299999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1579191656434067</v>
       </c>
       <c r="U2">
-        <v>1992</v>
+        <v>10095.4</v>
       </c>
       <c r="V2">
-        <v>1.921481624385068</v>
+        <v>1.247624108654547</v>
       </c>
       <c r="W2">
-        <v>0.06340536689622417</v>
+        <v>0.09208234098675122</v>
       </c>
       <c r="X2">
-        <v>0.5394781954200573</v>
+        <v>0.3281444345167849</v>
       </c>
       <c r="Y2">
-        <v>-0.4760728285238331</v>
+        <v>-0.2360620935300337</v>
       </c>
       <c r="Z2">
-        <v>0.1238351625595361</v>
+        <v>0.1666524701873935</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1538550080513593</v>
+        <v>0.1375631490294733</v>
       </c>
       <c r="AC2">
-        <v>-0.1538550080513593</v>
+        <v>-0.1375631490294733</v>
       </c>
       <c r="AD2">
-        <v>10101</v>
+        <v>18856.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10101</v>
+        <v>18856.3</v>
       </c>
       <c r="AG2">
-        <v>8109</v>
+        <v>8760.9</v>
       </c>
       <c r="AH2">
-        <v>0.9069197410596442</v>
+        <v>0.6997291079115333</v>
       </c>
       <c r="AI2">
-        <v>0.6806603773584906</v>
+        <v>0.6538381519726485</v>
       </c>
       <c r="AJ2">
-        <v>0.8866461834523327</v>
+        <v>0.5198545031627168</v>
       </c>
       <c r="AK2">
-        <v>0.6311488169364882</v>
+        <v>0.4673975672215109</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,117 +701,724 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>The National Bank of Bahrain B.S.C. (BAX:NBB)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.11</v>
+      </c>
+      <c r="E3">
+        <v>0.0386</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>227.6</v>
+      </c>
+      <c r="L3">
+        <v>0.4573954983922829</v>
+      </c>
+      <c r="M3">
+        <v>180.4</v>
+      </c>
+      <c r="N3">
+        <v>0.06126676855153677</v>
+      </c>
+      <c r="O3">
+        <v>0.7926186291739895</v>
+      </c>
+      <c r="P3">
+        <v>180.4</v>
+      </c>
+      <c r="Q3">
+        <v>0.06126676855153677</v>
+      </c>
+      <c r="R3">
+        <v>0.7926186291739895</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>2552.9</v>
+      </c>
+      <c r="V3">
+        <v>0.8670062829003227</v>
+      </c>
+      <c r="W3">
+        <v>0.1546510837806618</v>
+      </c>
+      <c r="X3">
+        <v>0.1099337794863243</v>
+      </c>
+      <c r="Y3">
+        <v>0.04471730429433751</v>
+      </c>
+      <c r="Z3">
+        <v>1.111458566004021</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.1105980294721194</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1105980294721194</v>
+      </c>
+      <c r="AD3">
+        <v>1164.8</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>1164.8</v>
+      </c>
+      <c r="AG3">
+        <v>-1388.1</v>
+      </c>
+      <c r="AH3">
+        <v>0.2834546029737425</v>
+      </c>
+      <c r="AI3">
+        <v>0.4306259011423713</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.8918658442559755</v>
+      </c>
+      <c r="AK3">
+        <v>-9.132236842105277</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bank of Bahrain and Kuwait B.S.C. (BAX:BBK)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0282</v>
+      </c>
+      <c r="E4">
+        <v>-0.00873</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>188.3</v>
+      </c>
+      <c r="L4">
+        <v>0.4815856777493606</v>
+      </c>
+      <c r="M4">
+        <v>151.2</v>
+      </c>
+      <c r="N4">
+        <v>0.06551126516464471</v>
+      </c>
+      <c r="O4">
+        <v>0.8029739776951672</v>
+      </c>
+      <c r="P4">
+        <v>151.2</v>
+      </c>
+      <c r="Q4">
+        <v>0.06551126516464471</v>
+      </c>
+      <c r="R4">
+        <v>0.8029739776951672</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2521.6</v>
+      </c>
+      <c r="V4">
+        <v>1.092547660311958</v>
+      </c>
+      <c r="W4">
+        <v>0.1207593150772783</v>
+      </c>
+      <c r="X4">
+        <v>0.1267723746665634</v>
+      </c>
+      <c r="Y4">
+        <v>-0.006013059589285163</v>
+      </c>
+      <c r="Z4">
+        <v>0.3186114732724903</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.1205037331529609</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1205037331529609</v>
+      </c>
+      <c r="AD4">
+        <v>1758.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1758.7</v>
+      </c>
+      <c r="AG4">
+        <v>-762.8999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.4324636683305875</v>
+      </c>
+      <c r="AI4">
+        <v>0.5197257602175005</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.4937544495501908</v>
+      </c>
+      <c r="AK4">
+        <v>-0.884726893192624</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Al Salam Bank B.S.C. (BAX:SALAM)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.283</v>
+      </c>
+      <c r="E5">
+        <v>0.193</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>142.1</v>
+      </c>
+      <c r="L5">
+        <v>0.2848266185608339</v>
+      </c>
+      <c r="M5">
+        <v>60.44</v>
+      </c>
+      <c r="N5">
+        <v>0.0426896454301455</v>
+      </c>
+      <c r="O5">
+        <v>0.4253342716396903</v>
+      </c>
+      <c r="P5">
+        <v>53.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.03785845458398079</v>
+      </c>
+      <c r="R5">
+        <v>0.3771991555242787</v>
+      </c>
+      <c r="S5">
+        <v>6.839999999999996</v>
+      </c>
+      <c r="T5">
+        <v>0.1131700860357379</v>
+      </c>
+      <c r="U5">
+        <v>2327.1</v>
+      </c>
+      <c r="V5">
+        <v>1.643664359372793</v>
+      </c>
+      <c r="W5">
+        <v>0.1626602564102564</v>
+      </c>
+      <c r="X5">
+        <v>0.1608751705947463</v>
+      </c>
+      <c r="Y5">
+        <v>0.001785085815510068</v>
+      </c>
+      <c r="Z5">
+        <v>0.3452356238322607</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.1280806529191732</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1280806529191732</v>
+      </c>
+      <c r="AD5">
+        <v>2129.5</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>2129.5</v>
+      </c>
+      <c r="AG5">
+        <v>-197.5999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.6006543874989422</v>
+      </c>
+      <c r="AI5">
+        <v>0.6107319031776988</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1622065342308323</v>
+      </c>
+      <c r="AK5">
+        <v>-0.1703888936793998</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bahrain Islamic Bank B.S.C. (BAX:BISB)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0206</v>
+      </c>
+      <c r="E6">
+        <v>-0.101</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>14.9</v>
+      </c>
+      <c r="L6">
+        <v>0.1576719576719577</v>
+      </c>
+      <c r="M6">
+        <v>5.202999999999999</v>
+      </c>
+      <c r="N6">
+        <v>0.03195945945945945</v>
+      </c>
+      <c r="O6">
+        <v>0.3491946308724831</v>
+      </c>
+      <c r="P6">
+        <v>5.06</v>
+      </c>
+      <c r="Q6">
+        <v>0.03108108108108108</v>
+      </c>
+      <c r="R6">
+        <v>0.3395973154362416</v>
+      </c>
+      <c r="S6">
+        <v>0.1429999999999998</v>
+      </c>
+      <c r="T6">
+        <v>0.02748414376321349</v>
+      </c>
+      <c r="U6">
+        <v>289.9</v>
+      </c>
+      <c r="V6">
+        <v>1.78071253071253</v>
+      </c>
+      <c r="W6">
+        <v>0.03928288953335091</v>
+      </c>
+      <c r="X6">
+        <v>0.5816754600613476</v>
+      </c>
+      <c r="Y6">
+        <v>-0.5423925705279967</v>
+      </c>
+      <c r="Z6">
+        <v>0.05125284738041002</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.1470456451397733</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1470456451397733</v>
+      </c>
+      <c r="AD6">
+        <v>1735.6</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1735.6</v>
+      </c>
+      <c r="AG6">
+        <v>1445.7</v>
+      </c>
+      <c r="AH6">
+        <v>0.9142435735356089</v>
+      </c>
+      <c r="AI6">
+        <v>0.8174453654860588</v>
+      </c>
+      <c r="AJ6">
+        <v>0.8987876903947778</v>
+      </c>
+      <c r="AK6">
+        <v>0.7885779741449844</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Khaleeji Bank B.S.C. (BAX:KHALEEJI)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.298</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>17.6</v>
+      </c>
+      <c r="L7">
+        <v>0.2880523731587561</v>
+      </c>
+      <c r="M7">
+        <v>92.16</v>
+      </c>
+      <c r="N7">
+        <v>0.4116123269316659</v>
+      </c>
+      <c r="O7">
+        <v>5.236363636363635</v>
+      </c>
+      <c r="P7">
+        <v>7.96</v>
+      </c>
+      <c r="Q7">
+        <v>0.03555158552925413</v>
+      </c>
+      <c r="R7">
+        <v>0.4522727272727272</v>
+      </c>
+      <c r="S7">
+        <v>84.2</v>
+      </c>
+      <c r="T7">
+        <v>0.9136284722222223</v>
+      </c>
+      <c r="U7">
+        <v>411.9</v>
+      </c>
+      <c r="V7">
+        <v>1.839660562751228</v>
+      </c>
+      <c r="W7">
+        <v>0.04397801099450276</v>
+      </c>
+      <c r="X7">
+        <v>0.4954136984388234</v>
+      </c>
+      <c r="Y7">
+        <v>-0.4514356874443206</v>
+      </c>
+      <c r="Z7">
+        <v>0.03367875647668394</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.1514373564814313</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1514373564814313</v>
+      </c>
+      <c r="AD7">
+        <v>1966.7</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>1966.7</v>
+      </c>
+      <c r="AG7">
+        <v>1554.8</v>
+      </c>
+      <c r="AH7">
+        <v>0.897790559664019</v>
+      </c>
+      <c r="AI7">
+        <v>0.8548639485351648</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8741215494462248</v>
+      </c>
+      <c r="AK7">
+        <v>0.8232117329379997</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Arab Banking Corporation (B.S.C.) (BAX:ABC)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D8">
         <v>0.0851</v>
       </c>
-      <c r="E3">
+      <c r="E8">
         <v>0.0553</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>267</v>
       </c>
-      <c r="L3">
+      <c r="L8">
         <v>0.2232441471571906</v>
       </c>
-      <c r="M3">
+      <c r="M8">
         <v>88</v>
       </c>
-      <c r="N3">
+      <c r="N8">
         <v>0.08488473039452107</v>
       </c>
-      <c r="O3">
+      <c r="O8">
         <v>0.3295880149812734</v>
       </c>
-      <c r="P3">
+      <c r="P8">
         <v>88</v>
       </c>
-      <c r="Q3">
+      <c r="Q8">
         <v>0.08488473039452107</v>
       </c>
-      <c r="R3">
+      <c r="R8">
         <v>0.3295880149812734</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
         <v>1992</v>
       </c>
-      <c r="V3">
+      <c r="V8">
         <v>1.921481624385068</v>
       </c>
-      <c r="W3">
+      <c r="W8">
         <v>0.06340536689622417</v>
       </c>
-      <c r="X3">
-        <v>0.5394781954200573</v>
-      </c>
-      <c r="Y3">
-        <v>-0.4760728285238331</v>
-      </c>
-      <c r="Z3">
+      <c r="X8">
+        <v>0.5395111800931895</v>
+      </c>
+      <c r="Y8">
+        <v>-0.4761058131969654</v>
+      </c>
+      <c r="Z8">
         <v>0.1238351625595361</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.1538550080513593</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1538550080513593</v>
-      </c>
-      <c r="AD3">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.1538580782732756</v>
+      </c>
+      <c r="AC8">
+        <v>-0.1538580782732756</v>
+      </c>
+      <c r="AD8">
         <v>10101</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>10101</v>
       </c>
-      <c r="AG3">
+      <c r="AG8">
         <v>8109</v>
       </c>
-      <c r="AH3">
+      <c r="AH8">
         <v>0.9069197410596442</v>
       </c>
-      <c r="AI3">
+      <c r="AI8">
         <v>0.6806603773584906</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ8">
         <v>0.8866461834523327</v>
       </c>
-      <c r="AK3">
+      <c r="AK8">
         <v>0.6311488169364882</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>
